--- a/diseases/d157/2015-2019.xlsx
+++ b/diseases/d157/2015-2019.xlsx
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18696,7 +18696,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24198,7 +24198,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -26163,7 +26163,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27735,7 +27735,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28521,7 +28521,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29307,7 +29307,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30093,7 +30093,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30879,7 +30879,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31665,7 +31665,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32451,7 +32451,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33237,7 +33237,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -34023,7 +34023,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34809,7 +34809,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35988,7 +35988,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -36774,7 +36774,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -37560,7 +37560,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -38346,7 +38346,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -39132,7 +39132,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -39918,7 +39918,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -40704,7 +40704,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -41490,7 +41490,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -42276,7 +42276,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -43062,7 +43062,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -43848,7 +43848,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -44634,7 +44634,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">

--- a/diseases/d157/2015-2019.xlsx
+++ b/diseases/d157/2015-2019.xlsx
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17910,7 +17910,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18696,7 +18696,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24198,7 +24198,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -26163,7 +26163,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -27735,7 +27735,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28521,7 +28521,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -29307,7 +29307,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30093,7 +30093,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30879,7 +30879,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31665,7 +31665,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -32451,7 +32451,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -33237,7 +33237,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -34023,7 +34023,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34809,7 +34809,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35988,7 +35988,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -36774,7 +36774,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -37560,7 +37560,7 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -38346,7 +38346,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -39132,7 +39132,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -39918,7 +39918,7 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN201" t="b">
@@ -40704,7 +40704,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -41490,7 +41490,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -42276,7 +42276,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -43062,7 +43062,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -43848,7 +43848,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -44634,7 +44634,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
